--- a/static/standards-correlations/Massachusetts_CS1_State_Standards.xlsx
+++ b/static/standards-correlations/Massachusetts_CS1_State_Standards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Crosswalk'!$A$4:$I$69</definedName>
@@ -565,10 +565,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scored against full lab bodies | C and Python tracks | Discovery Projects | Massachusetts DLCS Framework, adopted 2016 (voluntary)</t>
-        </is>
-      </c>
-    </row>
+          <t>Scored against full lab bodies | C and Python tracks | Introductory Projects | Massachusetts DLCS Framework, adopted 2016 (voluntary)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -602,7 +603,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Discovery Projects</t>
+          <t>Introductory Projects</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -690,7 +691,7 @@
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Discovery Systems 10 and 11 cover phishing and online conduct at an elementary level. Ext 5.3H (Find the Community) introduces collaborating with strangers in public repositories.</t>
+          <t>Introductory Systems 10 and 11 cover phishing and online conduct at an elementary level. Ext 5.3H (Find the Community) introduces collaborating with strangers in public repositories.</t>
         </is>
       </c>
     </row>
@@ -729,7 +730,7 @@
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>Discovery Systems 11 covers cyberbullying and age-appropriate responses at an elementary level.</t>
+          <t>Introductory Systems 11 covers cyberbullying and age-appropriate responses at an elementary level.</t>
         </is>
       </c>
     </row>
@@ -807,7 +808,7 @@
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>Discovery Systems 11 covers online conduct and motivations at an elementary level.</t>
+          <t>Introductory Systems 11 covers online conduct and motivations at an elementary level.</t>
         </is>
       </c>
     </row>
@@ -846,7 +847,7 @@
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>Team role rotation in Discovery Systems 13 addresses constructive group dynamics. Peer pressure is not named.</t>
+          <t>Team role rotation in Introductory Systems 13 addresses constructive group dynamics. Peer pressure is not named.</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1109,7 @@
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>Discovery Systems 12 covers how computing changed the world. Business and commerce specifically are not developed.</t>
+          <t>Introductory Systems 12 covers how computing changed the world. Business and commerce specifically are not developed.</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2118,7 @@
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>Discovery Systems 3 works through autonomous, semi-autonomous, and remote control, and Systems 8 runs a paired activity where one student is the software and one is the robot. Ext 4.2E (A Basic Building Block of AI) sharpens where the machine decides and the human specifies.</t>
+          <t>Introductory Systems 3 works through autonomous, semi-autonomous, and remote control, and Systems 8 runs a paired activity where one student is the software and one is the robot. Ext 4.2E (A Basic Building Block of AI) sharpens where the machine decides and the human specifies.</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2165,7 @@
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
-          <t>Discovery Systems 9 covers senders, receivers, and protocols; Ext 5.3F (Talking to a Server) traces a real exchange. Topologies are absent.</t>
+          <t>Introductory Systems 9 covers senders, receivers, and protocols; Ext 5.3F (Talking to a Server) traces a real exchange. Topologies are absent.</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2212,7 @@
       </c>
       <c r="I41" s="8" t="inlineStr">
         <is>
-          <t>Ext 5.3G (Secret Messages / HTTPS) covers credential exposure and its response; Discovery Systems 10 covers phishing and personal information. Identity theft and cyberattacks are absent.</t>
+          <t>Ext 5.3G (Secret Messages / HTTPS) covers credential exposure and its response; Introductory Systems 10 covers phishing and personal information. Identity theft and cyberattacks are absent.</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2490,7 @@
       </c>
       <c r="I47" s="8" t="inlineStr">
         <is>
-          <t>Flowcharting is taught in Discovery Systems 4 and Ext 1.2B (Dependency Map) produces a structure diagram. Formal pseudocode notation is not taught.</t>
+          <t>Flowcharting is taught in Introductory Systems 4 and Ext 1.2B (Dependency Map) produces a structure diagram. Formal pseudocode notation is not taught.</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2834,7 @@
       </c>
       <c r="I55" s="8" t="inlineStr">
         <is>
-          <t>Trial data is collected and interpreted as a team and Discovery Systems 13 asks what a team loses without varied input. Identifying which problems benefit is not a stated task.</t>
+          <t>Trial data is collected and interpreted as a team and Introductory Systems 13 asks what a team loses without varied input. Identifying which problems benefit is not a stated task.</t>
         </is>
       </c>
     </row>
@@ -3509,6 +3510,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -3553,7 +3555,7 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Coding strand, project NN (01-17).</t>
+          <t>Introductory Project, Coding strand, project NN (01-17).</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3567,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Systems strand, project NN (01-14).</t>
+          <t>Introductory Project, Systems strand, project NN (01-14).</t>
         </is>
       </c>
     </row>
@@ -3665,6 +3667,8 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
@@ -3682,7 +3686,7 @@
 SOURCE NOTE: Standard codes and statements were transcribed from the CodeHS published Massachusetts 9-12 framework. Verify wording against the official DESE DLCS Framework before using this crosswalk in any formal submission. One source statement (9-12.CAS.c5) begins 'nalyze' in the listing; corrected to 'Analyze' here.
 Crosswalk analysis (c) KIPR / Botball Explorer.
 === METHODOLOGY (revised) ===
-Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Discovery projects.
+Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Introductory projects.
 Scoring rule: Full requires evidence in the core lab flow. Partial is assigned where the only evidence sits in an optional Extension Challenge (labelled 'Finished early?'), or where the standard is only partly met.</t>
         </is>
       </c>
